--- a/events/Racice_2016_WC/Racice_2016_WC_Results.xlsx
+++ b/events/Racice_2016_WC/Racice_2016_WC_Results.xlsx
@@ -7051,6 +7051,11 @@
           <t>56986</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7111,6 +7116,11 @@
           <t>0:02:02.452</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>42349</t>
+        </is>
+      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>42337</t>
@@ -11689,6 +11699,11 @@
           <t>0:00:52.357</t>
         </is>
       </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>42346</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14019,6 +14034,11 @@
           <t>42336</t>
         </is>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>42356</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -27273,6 +27293,11 @@
           <t>42336</t>
         </is>
       </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>42356</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -42813,6 +42838,11 @@
           <t>0:00:36.528</t>
         </is>
       </c>
+      <c r="R634" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -51404,6 +51434,16 @@
           <t>42844</t>
         </is>
       </c>
+      <c r="S761" t="inlineStr">
+        <is>
+          <t>42349</t>
+        </is>
+      </c>
+      <c r="T761" t="inlineStr">
+        <is>
+          <t>42346</t>
+        </is>
+      </c>
       <c r="U761" t="inlineStr">
         <is>
           <t>42337</t>
@@ -51644,6 +51684,11 @@
           <t>47908</t>
         </is>
       </c>
+      <c r="U764" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -57591,6 +57636,11 @@
           <t>0:00:39.139</t>
         </is>
       </c>
+      <c r="R856" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -63456,6 +63506,11 @@
           <t>47908</t>
         </is>
       </c>
+      <c r="U946" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
@@ -75506,6 +75561,16 @@
           <t>42844</t>
         </is>
       </c>
+      <c r="S1125" t="inlineStr">
+        <is>
+          <t>42349</t>
+        </is>
+      </c>
+      <c r="T1125" t="inlineStr">
+        <is>
+          <t>42346</t>
+        </is>
+      </c>
       <c r="U1125" t="inlineStr">
         <is>
           <t>42337</t>
@@ -75834,6 +75899,11 @@
           <t>47908</t>
         </is>
       </c>
+      <c r="U1129" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
@@ -77336,6 +77406,16 @@
           <t>42844</t>
         </is>
       </c>
+      <c r="S1151" t="inlineStr">
+        <is>
+          <t>42349</t>
+        </is>
+      </c>
+      <c r="T1151" t="inlineStr">
+        <is>
+          <t>42346</t>
+        </is>
+      </c>
       <c r="U1151" t="inlineStr">
         <is>
           <t>42337</t>
@@ -77416,6 +77496,11 @@
           <t>47908</t>
         </is>
       </c>
+      <c r="U1152" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
@@ -79071,6 +79156,11 @@
           <t>47908</t>
         </is>
       </c>
+      <c r="U1173" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
@@ -80849,6 +80939,16 @@
           <t>42844</t>
         </is>
       </c>
+      <c r="S1196" t="inlineStr">
+        <is>
+          <t>42349</t>
+        </is>
+      </c>
+      <c r="T1196" t="inlineStr">
+        <is>
+          <t>42346</t>
+        </is>
+      </c>
       <c r="U1196" t="inlineStr">
         <is>
           <t>42337</t>
@@ -81011,6 +81111,11 @@
       <c r="T1198" t="inlineStr">
         <is>
           <t>47908</t>
+        </is>
+      </c>
+      <c r="U1198" t="inlineStr">
+        <is>
+          <t>47909</t>
         </is>
       </c>
     </row>
@@ -87160,7 +87265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D412"/>
+  <dimension ref="A1:D417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -96227,6 +96332,116 @@
         </is>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Alexandra Borbala</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>KERESZTESI</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>42349</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Amalie Ringtved</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>THOMSEN</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>42346</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Ida</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>VILLUMSEN</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>42356</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Nils Jensen</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>BOE</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Racice_2016_WC/Racice_2016_WC_Results.xlsx
+++ b/events/Racice_2016_WC/Racice_2016_WC_Results.xlsx
@@ -3787,6 +3787,11 @@
           <t>0:03:53.246</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9675,6 +9680,11 @@
           <t>0:00:34.134</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>51938</t>
+        </is>
+      </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>46414</t>
@@ -14729,6 +14739,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -15004,6 +15019,11 @@
           <t>53227</t>
         </is>
       </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -16184,6 +16204,11 @@
           <t>0:00:38.977</t>
         </is>
       </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>46375</t>
@@ -16324,6 +16349,11 @@
           <t>49674</t>
         </is>
       </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -19393,6 +19423,11 @@
           <t>0:03:50.366</t>
         </is>
       </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -23418,6 +23453,11 @@
           <t>0:00:32.944</t>
         </is>
       </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>51938</t>
+        </is>
+      </c>
       <c r="S346" t="inlineStr">
         <is>
           <t>46414</t>
@@ -27993,6 +28033,11 @@
           <t>53227</t>
         </is>
       </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -28268,6 +28313,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -31731,6 +31781,11 @@
           <t>0:00:33.396</t>
         </is>
       </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>51938</t>
+        </is>
+      </c>
       <c r="S470" t="inlineStr">
         <is>
           <t>46414</t>
@@ -33935,6 +33990,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -38561,6 +38621,11 @@
           <t>53227</t>
         </is>
       </c>
+      <c r="S570" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -39194,6 +39259,11 @@
           <t>0:00:37.462</t>
         </is>
       </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
       <c r="S579" t="inlineStr">
         <is>
           <t>46375</t>
@@ -39482,6 +39552,11 @@
           <t>49674</t>
         </is>
       </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -40053,6 +40128,11 @@
           <t>52199</t>
         </is>
       </c>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -40454,6 +40534,11 @@
           <t>0:00:36.278</t>
         </is>
       </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>51938</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -44198,6 +44283,11 @@
           <t>0:00:42.288</t>
         </is>
       </c>
+      <c r="R655" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -50434,6 +50524,11 @@
           <t>54302</t>
         </is>
       </c>
+      <c r="U748" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -50579,6 +50674,11 @@
           <t>54578</t>
         </is>
       </c>
+      <c r="S750" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
       <c r="T750" t="inlineStr">
         <is>
           <t>54525</t>
@@ -51044,6 +51144,11 @@
           <t>52199</t>
         </is>
       </c>
+      <c r="S756" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
       <c r="T756" t="inlineStr">
         <is>
           <t>52198</t>
@@ -56406,6 +56511,11 @@
           <t>0:01:58.664</t>
         </is>
       </c>
+      <c r="R837" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -57956,6 +58066,11 @@
           <t>0:00:38.511</t>
         </is>
       </c>
+      <c r="R861" t="inlineStr">
+        <is>
+          <t>51938</t>
+        </is>
+      </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -60346,6 +60461,11 @@
           <t>0:00:43.679</t>
         </is>
       </c>
+      <c r="R898" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -63576,6 +63696,11 @@
           <t>52199</t>
         </is>
       </c>
+      <c r="S947" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
       <c r="T947" t="inlineStr">
         <is>
           <t>52198</t>
@@ -66664,6 +66789,11 @@
           <t>0:01:48.516</t>
         </is>
       </c>
+      <c r="R994" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
@@ -68443,6 +68573,11 @@
           <t>0:00:37.281</t>
         </is>
       </c>
+      <c r="R1021" t="inlineStr">
+        <is>
+          <t>51938</t>
+        </is>
+      </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
@@ -68901,6 +69036,11 @@
           <t>0:00:42.479</t>
         </is>
       </c>
+      <c r="R1028" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
@@ -71480,6 +71620,11 @@
           <t>0:01:50.885</t>
         </is>
       </c>
+      <c r="R1067" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
@@ -75094,6 +75239,11 @@
           <t>54302</t>
         </is>
       </c>
+      <c r="U1119" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
@@ -75971,6 +76121,11 @@
           <t>52199</t>
         </is>
       </c>
+      <c r="S1130" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
       <c r="T1130" t="inlineStr">
         <is>
           <t>52198</t>
@@ -80303,6 +80458,11 @@
           <t>46375</t>
         </is>
       </c>
+      <c r="T1188" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
       <c r="U1188" t="inlineStr">
         <is>
           <t>46397</t>
@@ -80467,6 +80627,11 @@
           <t>35917</t>
         </is>
       </c>
+      <c r="U1190" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
@@ -82680,6 +82845,11 @@
           <t>0:20:44.529</t>
         </is>
       </c>
+      <c r="R1219" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
@@ -82740,6 +82910,11 @@
       <c r="P1220" t="inlineStr">
         <is>
           <t>0:21:08.335</t>
+        </is>
+      </c>
+      <c r="R1220" t="inlineStr">
+        <is>
+          <t>46407</t>
         </is>
       </c>
     </row>
@@ -87265,7 +87440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D417"/>
+  <dimension ref="A1:D425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -96442,6 +96617,182 @@
         </is>
       </c>
     </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>DRAHOKOUPIL</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Miika</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>NYKAENEN</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Vitaliy</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>VERHELES</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Vitalii</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>TSURKAN</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Mads Brandt</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>PEDERSEN</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>51938</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Kyrylo</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>CHERNOMOROV</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>63925</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Mate</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>GYORGJAKAB</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>158049</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Ji</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>WANG</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
